--- a/data/seed/2026-07/export_20260731_0612.xlsx
+++ b/data/seed/2026-07/export_20260731_0612.xlsx
@@ -38,40 +38,67 @@
     <t>Branch</t>
   </si>
   <si>
-    <t>AIBL-2026-982744</t>
+    <t>AIBL-2026-662870</t>
   </si>
   <si>
     <t>New Business</t>
   </si>
   <si>
+    <t>Policy Issuance - Single Premium</t>
+  </si>
+  <si>
+    <t>Completed - STP</t>
+  </si>
+  <si>
+    <t>Galway</t>
+  </si>
+  <si>
+    <t>AIBL-2026-214291</t>
+  </si>
+  <si>
     <t>Policy Issuance - Regular Premium</t>
   </si>
   <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>AIBL-2026-583009</t>
+  </si>
+  <si>
+    <t>Underwriting</t>
+  </si>
+  <si>
+    <t>Medical UW</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>AIBL-2026-292004</t>
+  </si>
+  <si>
+    <t>Standard UW Decision</t>
+  </si>
+  <si>
     <t>Completed - Manual</t>
   </si>
   <si>
-    <t>Galway</t>
-  </si>
-  <si>
-    <t>AIBL-2026-268602</t>
-  </si>
-  <si>
-    <t>Completed - STP</t>
-  </si>
-  <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>AIBL-2026-214291</t>
-  </si>
-  <si>
-    <t>Dublin</t>
-  </si>
-  <si>
-    <t>AIBL-2026-102165</t>
-  </si>
-  <si>
-    <t>Policy Issuance - Single Premium</t>
+    <t>AIBL-2026-948609</t>
+  </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Income Protection Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-506307</t>
+  </si>
+  <si>
+    <t>Endorsement</t>
+  </si>
+  <si>
+    <t>Beneficiary Change</t>
   </si>
   <si>
     <t>Waterford</t>
@@ -80,436 +107,400 @@
     <t>AIBL-2026-592993</t>
   </si>
   <si>
-    <t>Endorsement</t>
-  </si>
-  <si>
     <t>Address Change</t>
   </si>
   <si>
-    <t>AIBL-2026-713782</t>
-  </si>
-  <si>
-    <t>AIBL-2026-378529</t>
-  </si>
-  <si>
     <t>Cork</t>
   </si>
   <si>
-    <t>AIBL-2026-338384</t>
-  </si>
-  <si>
-    <t>Underwriting</t>
+    <t>AIBL-2026-710857</t>
+  </si>
+  <si>
+    <t>Policy Issuance</t>
+  </si>
+  <si>
+    <t>AIBL-2026-254132</t>
+  </si>
+  <si>
+    <t>AIBL-2026-408589</t>
+  </si>
+  <si>
+    <t>AIBL-2026-511682</t>
+  </si>
+  <si>
+    <t>Critical Illness Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-513691</t>
+  </si>
+  <si>
+    <t>AIBL-2026-194708</t>
+  </si>
+  <si>
+    <t>AIBL-2026-822653</t>
+  </si>
+  <si>
+    <t>AIBL-2026-270894</t>
+  </si>
+  <si>
+    <t>Maturity Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-449292</t>
+  </si>
+  <si>
+    <t>AIBL-2026-249834</t>
+  </si>
+  <si>
+    <t>Death Claim</t>
+  </si>
+  <si>
+    <t>AIBL-2026-177681</t>
+  </si>
+  <si>
+    <t>Premium Frequency Change</t>
+  </si>
+  <si>
+    <t>AIBL-2026-486770</t>
+  </si>
+  <si>
+    <t>Sum Assured Alteration</t>
+  </si>
+  <si>
+    <t>AIBL-2026-499539</t>
+  </si>
+  <si>
+    <t>AIBL-2026-100108</t>
+  </si>
+  <si>
+    <t>AIBL-2026-593568</t>
+  </si>
+  <si>
+    <t>AIBL-2026-485733</t>
+  </si>
+  <si>
+    <t>AIBL-2026-853977</t>
+  </si>
+  <si>
+    <t>Completed - Rework Required</t>
+  </si>
+  <si>
+    <t>AIBL-2026-767397</t>
+  </si>
+  <si>
+    <t>AIBL-2026-106657</t>
+  </si>
+  <si>
+    <t>AIBL-2026-461317</t>
+  </si>
+  <si>
+    <t>AIBL-2026-658160</t>
+  </si>
+  <si>
+    <t>AIBL-2026-516196</t>
+  </si>
+  <si>
+    <t>AIBL-2026-606783</t>
+  </si>
+  <si>
+    <t>AIBL-2026-876232</t>
+  </si>
+  <si>
+    <t>AIBL-2026-261122</t>
+  </si>
+  <si>
+    <t>AIBL-2026-239901</t>
+  </si>
+  <si>
+    <t>AIBL-2026-449255</t>
+  </si>
+  <si>
+    <t>AIBL-2026-875830</t>
+  </si>
+  <si>
+    <t>AIBL-2026-571636</t>
+  </si>
+  <si>
+    <t>AIBL-2026-596576</t>
+  </si>
+  <si>
+    <t>AIBL-2026-893682</t>
+  </si>
+  <si>
+    <t>AIBL-2026-776656</t>
+  </si>
+  <si>
+    <t>AIBL-2026-402867</t>
+  </si>
+  <si>
+    <t>AIBL-2026-872746</t>
+  </si>
+  <si>
+    <t>AIBL-2026-832847</t>
+  </si>
+  <si>
+    <t>AIBL-2026-246832</t>
+  </si>
+  <si>
+    <t>AIBL-2026-257910</t>
+  </si>
+  <si>
+    <t>AIBL-2026-662215</t>
   </si>
   <si>
     <t>Financial UW</t>
   </si>
   <si>
-    <t>AIBL-2026-408589</t>
-  </si>
-  <si>
-    <t>Standard UW Decision</t>
-  </si>
-  <si>
-    <t>AIBL-2026-751320</t>
-  </si>
-  <si>
-    <t>AIBL-2026-994280</t>
-  </si>
-  <si>
-    <t>AIBL-2026-822653</t>
-  </si>
-  <si>
-    <t>AIBL-2026-270894</t>
-  </si>
-  <si>
-    <t>Claim</t>
-  </si>
-  <si>
-    <t>Maturity Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-249834</t>
-  </si>
-  <si>
-    <t>Death Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-188303</t>
-  </si>
-  <si>
-    <t>Sum Assured Alteration</t>
-  </si>
-  <si>
-    <t>AIBL-2026-422950</t>
-  </si>
-  <si>
-    <t>AIBL-2026-837933</t>
-  </si>
-  <si>
-    <t>AIBL-2026-275070</t>
-  </si>
-  <si>
-    <t>AIBL-2026-480259</t>
-  </si>
-  <si>
-    <t>AIBL-2026-762782</t>
-  </si>
-  <si>
-    <t>AIBL-2026-106657</t>
-  </si>
-  <si>
-    <t>Medical UW</t>
-  </si>
-  <si>
-    <t>AIBL-2026-461317</t>
-  </si>
-  <si>
-    <t>AIBL-2026-844323</t>
-  </si>
-  <si>
-    <t>AIBL-2026-658160</t>
-  </si>
-  <si>
-    <t>AIBL-2026-975589</t>
-  </si>
-  <si>
-    <t>AIBL-2026-853095</t>
-  </si>
-  <si>
-    <t>AIBL-2026-763970</t>
-  </si>
-  <si>
-    <t>Premium Frequency Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-600426</t>
-  </si>
-  <si>
-    <t>Beneficiary Change</t>
-  </si>
-  <si>
-    <t>AIBL-2026-207430</t>
-  </si>
-  <si>
-    <t>AIBL-2026-728473</t>
-  </si>
-  <si>
-    <t>Policy Issuance</t>
-  </si>
-  <si>
-    <t>AIBL-2026-239901</t>
-  </si>
-  <si>
-    <t>AIBL-2026-422742</t>
-  </si>
-  <si>
-    <t>AIBL-2026-726210</t>
-  </si>
-  <si>
-    <t>AIBL-2026-251287</t>
-  </si>
-  <si>
-    <t>AIBL-2026-161818</t>
-  </si>
-  <si>
-    <t>AIBL-2026-901526</t>
-  </si>
-  <si>
-    <t>AIBL-2026-712953</t>
-  </si>
-  <si>
-    <t>Income Protection Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-793802</t>
-  </si>
-  <si>
-    <t>AIBL-2026-854282</t>
-  </si>
-  <si>
-    <t>AIBL-2026-175638</t>
-  </si>
-  <si>
-    <t>AIBL-2026-100065</t>
-  </si>
-  <si>
-    <t>AIBL-2026-726236</t>
-  </si>
-  <si>
-    <t>Critical Illness Claim</t>
-  </si>
-  <si>
-    <t>AIBL-2026-754219</t>
-  </si>
-  <si>
-    <t>AIBL-2026-317811</t>
-  </si>
-  <si>
-    <t>AIBL-2026-956232</t>
+    <t>AIBL-2026-589556</t>
   </si>
   <si>
     <t>AIBL-2026-523461</t>
   </si>
   <si>
-    <t>AIBL-2026-131558</t>
+    <t>AIBL-2026-326264</t>
+  </si>
+  <si>
+    <t>AIBL-2026-134105</t>
   </si>
   <si>
     <t>AIBL-2026-740190</t>
   </si>
   <si>
-    <t>AIBL-2026-378148</t>
+    <t>AIBL-2026-706583</t>
+  </si>
+  <si>
+    <t>AIBL-2026-938707</t>
   </si>
   <si>
     <t>AIBL-2026-240770</t>
   </si>
   <si>
+    <t>AIBL-2026-889786</t>
+  </si>
+  <si>
     <t>AIBL-2026-179738</t>
   </si>
   <si>
-    <t>AIBL-2026-300543</t>
-  </si>
-  <si>
     <t>AIBL-2026-775020</t>
   </si>
   <si>
-    <t>AIBL-2026-953364</t>
-  </si>
-  <si>
-    <t>AIBL-2026-938241</t>
-  </si>
-  <si>
-    <t>AIBL-2026-710876</t>
+    <t>AIBL-2026-453735</t>
   </si>
   <si>
     <t>AIBL-2026-630831</t>
   </si>
   <si>
-    <t>AIBL-2026-325189</t>
-  </si>
-  <si>
-    <t>AIBL-2026-578606</t>
-  </si>
-  <si>
-    <t>AIBL-2026-827016</t>
-  </si>
-  <si>
     <t>AIBL-2026-518474</t>
   </si>
   <si>
     <t>AIBL-2026-351947</t>
   </si>
   <si>
-    <t>AIBL-2026-855151</t>
-  </si>
-  <si>
-    <t>AIBL-2026-279372</t>
-  </si>
-  <si>
-    <t>AIBL-2026-129773</t>
-  </si>
-  <si>
-    <t>AIBL-2026-824528</t>
-  </si>
-  <si>
-    <t>AIBL-2026-437821</t>
-  </si>
-  <si>
-    <t>AIBL-2026-933106</t>
+    <t>AIBL-2026-865340</t>
+  </si>
+  <si>
+    <t>AIBL-2026-775669</t>
+  </si>
+  <si>
+    <t>AIBL-2026-405219</t>
+  </si>
+  <si>
+    <t>AIBL-2026-612982</t>
+  </si>
+  <si>
+    <t>AIBL-2026-458767</t>
+  </si>
+  <si>
+    <t>AIBL-2026-807062</t>
+  </si>
+  <si>
+    <t>AIBL-2026-567416</t>
+  </si>
+  <si>
+    <t>AIBL-2026-528761</t>
+  </si>
+  <si>
+    <t>AIBL-2026-755952</t>
+  </si>
+  <si>
+    <t>AIBL-2026-533947</t>
   </si>
   <si>
     <t>AIBL-2026-153510</t>
   </si>
   <si>
-    <t>AIBL-2026-853942</t>
-  </si>
-  <si>
-    <t>AIBL-2026-162339</t>
-  </si>
-  <si>
-    <t>AIBL-2026-160671</t>
-  </si>
-  <si>
-    <t>AIBL-2026-658817</t>
-  </si>
-  <si>
-    <t>AIBL-2026-764923</t>
+    <t>AIBL-2026-986772</t>
+  </si>
+  <si>
+    <t>AIBL-2026-988341</t>
+  </si>
+  <si>
+    <t>AIBL-2026-216677</t>
+  </si>
+  <si>
+    <t>AIBL-2026-904423</t>
+  </si>
+  <si>
+    <t>AIBL-2026-388749</t>
+  </si>
+  <si>
+    <t>AIBL-2026-430444</t>
   </si>
   <si>
     <t>AIBL-2026-458074</t>
   </si>
   <si>
-    <t>AIBL-2026-520954</t>
-  </si>
-  <si>
-    <t>Completed - Rework Required</t>
-  </si>
-  <si>
     <t>AIBL-2026-548559</t>
   </si>
   <si>
-    <t>AIBL-2026-364023</t>
-  </si>
-  <si>
-    <t>AIBL-2026-836039</t>
+    <t>AIBL-2026-194023</t>
+  </si>
+  <si>
+    <t>AIBL-2026-324097</t>
+  </si>
+  <si>
+    <t>AIBL-2026-134191</t>
   </si>
   <si>
     <t>AIBL-2026-922584</t>
   </si>
   <si>
-    <t>AIBL-2026-179063</t>
-  </si>
-  <si>
-    <t>AIBL-2026-324028</t>
-  </si>
-  <si>
-    <t>AIBL-2026-741564</t>
-  </si>
-  <si>
-    <t>AIBL-2026-891083</t>
-  </si>
-  <si>
-    <t>AIBL-2026-653811</t>
-  </si>
-  <si>
-    <t>AIBL-2026-803710</t>
-  </si>
-  <si>
-    <t>AIBL-2026-231441</t>
-  </si>
-  <si>
-    <t>AIBL-2026-312887</t>
-  </si>
-  <si>
-    <t>AIBL-2026-929075</t>
-  </si>
-  <si>
-    <t>AIBL-2026-359092</t>
-  </si>
-  <si>
-    <t>AIBL-2026-843089</t>
-  </si>
-  <si>
-    <t>AIBL-2026-426136</t>
-  </si>
-  <si>
-    <t>AIBL-2026-587357</t>
-  </si>
-  <si>
-    <t>AIBL-2026-804927</t>
-  </si>
-  <si>
-    <t>AIBL-2026-906940</t>
-  </si>
-  <si>
-    <t>AIBL-2026-143769</t>
-  </si>
-  <si>
-    <t>AIBL-2026-890544</t>
-  </si>
-  <si>
-    <t>AIBL-2026-429014</t>
-  </si>
-  <si>
-    <t>AIBL-2026-859355</t>
+    <t>AIBL-2026-921382</t>
+  </si>
+  <si>
+    <t>AIBL-2026-416198</t>
+  </si>
+  <si>
+    <t>AIBL-2026-739540</t>
+  </si>
+  <si>
+    <t>AIBL-2026-450296</t>
+  </si>
+  <si>
+    <t>AIBL-2026-220019</t>
+  </si>
+  <si>
+    <t>AIBL-2026-648532</t>
+  </si>
+  <si>
+    <t>AIBL-2026-832451</t>
+  </si>
+  <si>
+    <t>AIBL-2026-830607</t>
+  </si>
+  <si>
+    <t>AIBL-2026-197502</t>
   </si>
   <si>
     <t>AIBL-2026-495664</t>
   </si>
   <si>
-    <t>AIBL-2026-865601</t>
-  </si>
-  <si>
-    <t>AIBL-2026-900081</t>
-  </si>
-  <si>
-    <t>AIBL-2026-338229</t>
-  </si>
-  <si>
-    <t>AIBL-2026-550212</t>
-  </si>
-  <si>
-    <t>AIBL-2026-828286</t>
+    <t>AIBL-2026-813472</t>
+  </si>
+  <si>
+    <t>AIBL-2026-133409</t>
+  </si>
+  <si>
+    <t>AIBL-2026-544250</t>
+  </si>
+  <si>
+    <t>AIBL-2026-718361</t>
+  </si>
+  <si>
+    <t>AIBL-2026-848725</t>
+  </si>
+  <si>
+    <t>AIBL-2026-969315</t>
+  </si>
+  <si>
+    <t>AIBL-2026-463759</t>
+  </si>
+  <si>
+    <t>AIBL-2026-291223</t>
+  </si>
+  <si>
+    <t>AIBL-2026-942524</t>
+  </si>
+  <si>
+    <t>AIBL-2026-204854</t>
+  </si>
+  <si>
+    <t>AIBL-2026-565902</t>
+  </si>
+  <si>
+    <t>AIBL-2026-940469</t>
+  </si>
+  <si>
+    <t>AIBL-2026-454651</t>
   </si>
   <si>
     <t>AIBL-2026-139015</t>
   </si>
   <si>
-    <t>AIBL-2026-834169</t>
-  </si>
-  <si>
-    <t>AIBL-2026-119883</t>
-  </si>
-  <si>
-    <t>AIBL-2026-878368</t>
-  </si>
-  <si>
-    <t>AIBL-2026-679966</t>
-  </si>
-  <si>
-    <t>AIBL-2026-467106</t>
-  </si>
-  <si>
-    <t>AIBL-2026-728141</t>
-  </si>
-  <si>
-    <t>AIBL-2026-132565</t>
-  </si>
-  <si>
-    <t>AIBL-2026-430314</t>
+    <t>AIBL-2026-174017</t>
+  </si>
+  <si>
+    <t>AIBL-2026-250523</t>
+  </si>
+  <si>
+    <t>AIBL-2026-701103</t>
   </si>
   <si>
     <t>AIBL-2026-563642</t>
   </si>
   <si>
+    <t>AIBL-2026-403964</t>
+  </si>
+  <si>
     <t>AIBL-2026-780055</t>
   </si>
   <si>
-    <t>AIBL-2026-736646</t>
-  </si>
-  <si>
     <t>AIBL-2026-471991</t>
   </si>
   <si>
+    <t>AIBL-2026-187560</t>
+  </si>
+  <si>
     <t>AIBL-2026-918448</t>
   </si>
   <si>
-    <t>AIBL-2026-876387</t>
-  </si>
-  <si>
-    <t>AIBL-2026-646795</t>
-  </si>
-  <si>
-    <t>AIBL-2026-101639</t>
-  </si>
-  <si>
-    <t>AIBL-2026-978288</t>
-  </si>
-  <si>
-    <t>AIBL-2026-685509</t>
-  </si>
-  <si>
-    <t>AIBL-2026-422197</t>
-  </si>
-  <si>
-    <t>AIBL-2026-308151</t>
+    <t>AIBL-2026-174467</t>
+  </si>
+  <si>
+    <t>AIBL-2026-749020</t>
+  </si>
+  <si>
+    <t>AIBL-2026-728761</t>
+  </si>
+  <si>
+    <t>AIBL-2026-545810</t>
   </si>
   <si>
     <t>AIBL-2026-381936</t>
   </si>
   <si>
+    <t>AIBL-2026-595277</t>
+  </si>
+  <si>
     <t>AIBL-2026-277874</t>
   </si>
   <si>
-    <t>AIBL-2026-266810</t>
-  </si>
-  <si>
-    <t>AIBL-2026-268374</t>
+    <t>AIBL-2026-287845</t>
+  </si>
+  <si>
+    <t>AIBL-2026-209682</t>
+  </si>
+  <si>
+    <t>AIBL-2026-242701</t>
+  </si>
+  <si>
+    <t>AIBL-2026-323302</t>
   </si>
   <si>
     <t>AIBL-2026-647323</t>
   </si>
   <si>
-    <t>AIBL-2026-929486</t>
+    <t>AIBL-2026-106061</t>
   </si>
   <si>
     <t>AIBL-2026-646611</t>
@@ -518,31 +509,40 @@
     <t>AIBL-2026-494459</t>
   </si>
   <si>
-    <t>AIBL-2026-157962</t>
+    <t>AIBL-2026-517971</t>
   </si>
   <si>
     <t>AIBL-2026-302207</t>
   </si>
   <si>
-    <t>AIBL-2026-285662</t>
+    <t>AIBL-2026-146943</t>
+  </si>
+  <si>
+    <t>AIBL-2026-692090</t>
+  </si>
+  <si>
+    <t>AIBL-2026-743566</t>
   </si>
   <si>
     <t>AIBL-2026-216076</t>
   </si>
   <si>
-    <t>AIBL-2026-243685</t>
-  </si>
-  <si>
-    <t>AIBL-2026-826724</t>
-  </si>
-  <si>
-    <t>AIBL-2026-135125</t>
-  </si>
-  <si>
-    <t>AIBL-2026-276411</t>
-  </si>
-  <si>
-    <t>AIBL-2026-126141</t>
+    <t>AIBL-2026-233332</t>
+  </si>
+  <si>
+    <t>AIBL-2026-124267</t>
+  </si>
+  <si>
+    <t>AIBL-2026-991078</t>
+  </si>
+  <si>
+    <t>AIBL-2026-477106</t>
+  </si>
+  <si>
+    <t>AIBL-2026-196944</t>
+  </si>
+  <si>
+    <t>AIBL-2026-164733</t>
   </si>
   <si>
     <t>Source System</t>
@@ -1041,7 +1041,7 @@
         <v>46206</v>
       </c>
       <c r="F2" s="2">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1058,7 +1058,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1">
         <v>46204</v>
@@ -1067,10 +1067,10 @@
         <v>46210</v>
       </c>
       <c r="F3" s="2">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1081,10 +1081,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>46204</v>
@@ -1093,62 +1093,62 @@
         <v>46206</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>46204</v>
       </c>
       <c r="E5" s="1">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="F5" s="2">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1">
         <v>46204</v>
       </c>
       <c r="E6" s="1">
-        <v>46209</v>
+        <v>46215</v>
       </c>
       <c r="F6" s="2">
-        <v>5.4</v>
+        <v>10.8</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -1156,117 +1156,117 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E7" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="F7" s="2">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E8" s="1">
         <v>46210</v>
       </c>
       <c r="F8" s="2">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>46205</v>
       </c>
       <c r="E9" s="1">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="F9" s="2">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D10" s="1">
         <v>46205</v>
       </c>
       <c r="E10" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F10" s="2">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1">
         <v>46205</v>
@@ -1275,59 +1275,59 @@
         <v>46208</v>
       </c>
       <c r="F11" s="2">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D12" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E12" s="1">
-        <v>46208</v>
+        <v>46223</v>
       </c>
       <c r="F12" s="2">
-        <v>1.8</v>
+        <v>17.8</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
         <v>46206</v>
       </c>
       <c r="E13" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="F13" s="2">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1338,103 +1338,103 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1">
         <v>46206</v>
       </c>
       <c r="E14" s="1">
-        <v>46221</v>
+        <v>46208</v>
       </c>
       <c r="F14" s="2">
-        <v>15.1</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1">
         <v>46206</v>
       </c>
       <c r="E15" s="1">
-        <v>46213</v>
+        <v>46207</v>
       </c>
       <c r="F15" s="2">
-        <v>7.1</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1">
         <v>46206</v>
       </c>
       <c r="E16" s="1">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="F16" s="2">
-        <v>5.4</v>
+        <v>10.1</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="1">
         <v>46206</v>
       </c>
       <c r="E17" s="1">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="F17" s="2">
-        <v>3</v>
+        <v>10.2</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -1442,77 +1442,77 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D18" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E18" s="1">
-        <v>46216</v>
+        <v>46226</v>
       </c>
       <c r="F18" s="2">
-        <v>6.6</v>
+        <v>20.1</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D19" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E19" s="1">
-        <v>46215</v>
+        <v>46211</v>
       </c>
       <c r="F19" s="2">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E20" s="1">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="F20" s="2">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -1520,152 +1520,152 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1">
         <v>46209</v>
       </c>
       <c r="E21" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1">
         <v>46209</v>
       </c>
       <c r="E22" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="F22" s="2">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1">
         <v>46209</v>
       </c>
       <c r="E23" s="1">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="F23" s="2">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H23" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1">
         <v>46209</v>
       </c>
       <c r="E24" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="F24" s="2">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1">
         <v>46209</v>
       </c>
       <c r="E25" s="1">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="F25" s="2">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H25" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1">
         <v>46209</v>
       </c>
       <c r="E26" s="1">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="F26" s="2">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1676,389 +1676,389 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D27" s="1">
         <v>46209</v>
       </c>
       <c r="E27" s="1">
-        <v>46219</v>
+        <v>46213</v>
       </c>
       <c r="F27" s="2">
-        <v>10.2</v>
+        <v>3.8</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="D28" s="1">
         <v>46209</v>
       </c>
       <c r="E28" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="F28" s="2">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D29" s="1">
         <v>46209</v>
       </c>
       <c r="E29" s="1">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="F29" s="2">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
       </c>
       <c r="H29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1">
         <v>46209</v>
       </c>
       <c r="E30" s="1">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="F30" s="2">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="E31" s="1">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="F31" s="2">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D32" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="E32" s="1">
-        <v>46215</v>
+        <v>46211</v>
       </c>
       <c r="F32" s="2">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
       </c>
       <c r="H32" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D33" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="E33" s="1">
-        <v>46217</v>
+        <v>46215</v>
       </c>
       <c r="F33" s="2">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D34" s="1">
         <v>46210</v>
       </c>
       <c r="E34" s="1">
-        <v>46214</v>
+        <v>46213</v>
       </c>
       <c r="F34" s="2">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D35" s="1">
         <v>46210</v>
       </c>
       <c r="E35" s="1">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="F35" s="2">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H35" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1">
         <v>46210</v>
       </c>
       <c r="E36" s="1">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="F36" s="2">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D37" s="1">
         <v>46210</v>
       </c>
       <c r="E37" s="1">
-        <v>46212</v>
+        <v>46215</v>
       </c>
       <c r="F37" s="2">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D38" s="1">
         <v>46210</v>
       </c>
       <c r="E38" s="1">
-        <v>46227</v>
+        <v>46214</v>
       </c>
       <c r="F38" s="2">
-        <v>17.4</v>
+        <v>4.2</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D39" s="1">
         <v>46210</v>
       </c>
       <c r="E39" s="1">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="F39" s="2">
-        <v>21.5</v>
+        <v>2.2</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H39" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="D40" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E40" s="1">
-        <v>46228</v>
+        <v>46217</v>
       </c>
       <c r="F40" s="2">
-        <v>18</v>
+        <v>5.7</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
       </c>
       <c r="H40" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D41" s="1">
         <v>46211</v>
       </c>
       <c r="E41" s="1">
-        <v>46215</v>
+        <v>46212</v>
       </c>
       <c r="F41" s="2">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -2066,54 +2066,54 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D42" s="1">
         <v>46211</v>
       </c>
       <c r="E42" s="1">
-        <v>46221</v>
+        <v>46214</v>
       </c>
       <c r="F42" s="2">
-        <v>9.7</v>
+        <v>3.4</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D43" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="E43" s="1">
-        <v>46224</v>
+        <v>46215</v>
       </c>
       <c r="F43" s="2">
-        <v>12.8</v>
+        <v>2.5</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -2121,25 +2121,25 @@
         <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="E44" s="1">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="F44" s="2">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -2147,25 +2147,25 @@
         <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="E45" s="1">
-        <v>46214</v>
+        <v>46217</v>
       </c>
       <c r="F45" s="2">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H45" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2173,36 +2173,36 @@
         <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="D46" s="1">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="E46" s="1">
         <v>46214</v>
       </c>
       <c r="F46" s="2">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D47" s="1">
         <v>46212</v>
@@ -2211,362 +2211,362 @@
         <v>46215</v>
       </c>
       <c r="F47" s="2">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D48" s="1">
         <v>46212</v>
       </c>
       <c r="E48" s="1">
-        <v>46217</v>
+        <v>46215</v>
       </c>
       <c r="F48" s="2">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D49" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="E49" s="1">
-        <v>46218</v>
+        <v>46214</v>
       </c>
       <c r="F49" s="2">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="G49" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D50" s="1">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="E50" s="1">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="F50" s="2">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1">
         <v>46213</v>
       </c>
       <c r="E51" s="1">
-        <v>46222</v>
+        <v>46217</v>
       </c>
       <c r="F51" s="2">
-        <v>8.7</v>
+        <v>4</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C52" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D52" s="1">
         <v>46213</v>
       </c>
       <c r="E52" s="1">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="F52" s="2">
-        <v>12.8</v>
+        <v>5</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
       </c>
       <c r="H52" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="D53" s="1">
         <v>46213</v>
       </c>
       <c r="E53" s="1">
-        <v>46217</v>
+        <v>46215</v>
       </c>
       <c r="F53" s="2">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D54" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="E54" s="1">
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="F54" s="2">
-        <v>5.3</v>
+        <v>14.6</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H54" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D55" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="E55" s="1">
-        <v>46222</v>
+        <v>46227</v>
       </c>
       <c r="F55" s="2">
-        <v>6.3</v>
+        <v>14.2</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
       </c>
       <c r="H55" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D56" s="1">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="E56" s="1">
-        <v>46222</v>
+        <v>46232</v>
       </c>
       <c r="F56" s="2">
-        <v>6.4</v>
+        <v>18.7</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D57" s="1">
         <v>46216</v>
       </c>
       <c r="E57" s="1">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="F57" s="2">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
       </c>
       <c r="H57" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D58" s="1">
         <v>46216</v>
       </c>
       <c r="E58" s="1">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F58" s="2">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="G58" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H58" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D59" s="1">
         <v>46216</v>
       </c>
       <c r="E59" s="1">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="F59" s="2">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D60" s="1">
         <v>46216</v>
       </c>
       <c r="E60" s="1">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="F60" s="2">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="G60" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D61" s="1">
         <v>46216</v>
@@ -2575,76 +2575,76 @@
         <v>46220</v>
       </c>
       <c r="F61" s="2">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D62" s="1">
         <v>46216</v>
       </c>
       <c r="E62" s="1">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="F62" s="2">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H62" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="D63" s="1">
         <v>46216</v>
       </c>
       <c r="E63" s="1">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="F63" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
       </c>
       <c r="H63" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="D64" s="1">
         <v>46216</v>
@@ -2653,128 +2653,128 @@
         <v>46219</v>
       </c>
       <c r="F64" s="2">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H64" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D65" s="1">
         <v>46216</v>
       </c>
       <c r="E65" s="1">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="F65" s="2">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="G65" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H65" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D66" s="1">
         <v>46216</v>
       </c>
       <c r="E66" s="1">
-        <v>46233</v>
+        <v>46221</v>
       </c>
       <c r="F66" s="2">
-        <v>16.6</v>
+        <v>4.8</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D67" s="1">
         <v>46216</v>
       </c>
       <c r="E67" s="1">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="F67" s="2">
-        <v>9.2</v>
+        <v>11.2</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
       </c>
       <c r="H67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D68" s="1">
         <v>46216</v>
       </c>
       <c r="E68" s="1">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="F68" s="2">
-        <v>13.3</v>
+        <v>17.6</v>
       </c>
       <c r="G68" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D69" s="1">
         <v>46216</v>
@@ -2783,137 +2783,137 @@
         <v>46219</v>
       </c>
       <c r="F69" s="2">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G69" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H69" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="D70" s="1">
         <v>46216</v>
       </c>
       <c r="E70" s="1">
-        <v>46222</v>
+        <v>46221</v>
       </c>
       <c r="F70" s="2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G70" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H70" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D71" s="1">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="E71" s="1">
-        <v>46221</v>
+        <v>46218</v>
       </c>
       <c r="F71" s="2">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H71" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="D72" s="1">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="E72" s="1">
-        <v>46228</v>
+        <v>46222</v>
       </c>
       <c r="F72" s="2">
-        <v>11.4</v>
+        <v>5.6</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
       </c>
       <c r="H72" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>48</v>
+      </c>
+      <c r="D73" s="1">
+        <v>46216</v>
+      </c>
+      <c r="E73" s="1">
+        <v>46219</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="G73" t="s">
         <v>22</v>
       </c>
-      <c r="C73" t="s">
-        <v>57</v>
-      </c>
-      <c r="D73" s="1">
-        <v>46217</v>
-      </c>
-      <c r="E73" s="1">
-        <v>46222</v>
-      </c>
-      <c r="F73" s="2">
-        <v>5.2</v>
-      </c>
-      <c r="G73" t="s">
-        <v>14</v>
-      </c>
       <c r="H73" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
         <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D74" s="1">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="E74" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="F74" s="2">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -2924,39 +2924,39 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D75" s="1">
+        <v>46217</v>
+      </c>
+      <c r="E75" s="1">
         <v>46218</v>
       </c>
-      <c r="E75" s="1">
-        <v>46221</v>
-      </c>
       <c r="F75" s="2">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D76" s="1">
         <v>46218</v>
@@ -2965,39 +2965,39 @@
         <v>46222</v>
       </c>
       <c r="F76" s="2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G76" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H76" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D77" s="1">
         <v>46218</v>
       </c>
       <c r="E77" s="1">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="F77" s="2">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="G77" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="H77" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -3005,10 +3005,10 @@
         <v>110</v>
       </c>
       <c r="B78" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D78" s="1">
         <v>46218</v>
@@ -3017,13 +3017,13 @@
         <v>46220</v>
       </c>
       <c r="F78" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G78" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H78" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -3031,25 +3031,25 @@
         <v>111</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D79" s="1">
         <v>46218</v>
       </c>
       <c r="E79" s="1">
-        <v>46220</v>
+        <v>46222</v>
       </c>
       <c r="F79" s="2">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H79" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -3057,25 +3057,25 @@
         <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C80" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D80" s="1">
         <v>46218</v>
       </c>
       <c r="E80" s="1">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="F80" s="2">
-        <v>16.1</v>
+        <v>1.7</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -3083,22 +3083,22 @@
         <v>113</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C81" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D81" s="1">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="E81" s="1">
-        <v>46225</v>
+        <v>46222</v>
       </c>
       <c r="F81" s="2">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="G81" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -3109,25 +3109,25 @@
         <v>114</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D82" s="1">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="E82" s="1">
-        <v>46224</v>
+        <v>46235</v>
       </c>
       <c r="F82" s="2">
-        <v>5.2</v>
+        <v>17.3</v>
       </c>
       <c r="G82" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -3135,25 +3135,25 @@
         <v>115</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
         <v>48</v>
       </c>
       <c r="D83" s="1">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="E83" s="1">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="F83" s="2">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="G83" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H83" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -3161,25 +3161,25 @@
         <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D84" s="1">
         <v>46219</v>
       </c>
       <c r="E84" s="1">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F84" s="2">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="G84" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H84" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -3187,25 +3187,25 @@
         <v>117</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D85" s="1">
         <v>46219</v>
       </c>
       <c r="E85" s="1">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="F85" s="2">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -3216,19 +3216,19 @@
         <v>9</v>
       </c>
       <c r="C86" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D86" s="1">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="E86" s="1">
-        <v>46225</v>
+        <v>46221</v>
       </c>
       <c r="F86" s="2">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="G86" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -3239,25 +3239,25 @@
         <v>119</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D87" s="1">
         <v>46220</v>
       </c>
       <c r="E87" s="1">
-        <v>46225</v>
+        <v>46240</v>
       </c>
       <c r="F87" s="2">
-        <v>4.9</v>
+        <v>19.8</v>
       </c>
       <c r="G87" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H87" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -3271,19 +3271,19 @@
         <v>10</v>
       </c>
       <c r="D88" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E88" s="1">
         <v>46225</v>
       </c>
       <c r="F88" s="2">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="G88" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H88" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -3294,22 +3294,22 @@
         <v>9</v>
       </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D89" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E89" s="1">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="F89" s="2">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
       </c>
       <c r="H89" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -3317,25 +3317,25 @@
         <v>122</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D90" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E90" s="1">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="F90" s="2">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G90" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -3343,25 +3343,25 @@
         <v>123</v>
       </c>
       <c r="B91" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D91" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E91" s="1">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="F91" s="2">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G91" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H91" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -3369,25 +3369,25 @@
         <v>124</v>
       </c>
       <c r="B92" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" t="s">
+        <v>38</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46223</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46235</v>
+      </c>
+      <c r="F92" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="G92" t="s">
         <v>22</v>
       </c>
-      <c r="C92" t="s">
-        <v>55</v>
-      </c>
-      <c r="D92" s="1">
-        <v>46220</v>
-      </c>
-      <c r="E92" s="1">
-        <v>46222</v>
-      </c>
-      <c r="F92" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="G92" t="s">
-        <v>11</v>
-      </c>
       <c r="H92" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -3395,25 +3395,25 @@
         <v>125</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C93" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D93" s="1">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="E93" s="1">
-        <v>46222</v>
+        <v>46229</v>
       </c>
       <c r="F93" s="2">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="G93" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H93" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -3421,25 +3421,25 @@
         <v>126</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D94" s="1">
         <v>46223</v>
       </c>
       <c r="E94" s="1">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="F94" s="2">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="G94" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H94" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -3450,22 +3450,22 @@
         <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D95" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E95" s="1">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="F95" s="2">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="G95" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H95" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -3473,22 +3473,22 @@
         <v>128</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D96" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E96" s="1">
         <v>46229</v>
       </c>
       <c r="F96" s="2">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -3499,25 +3499,25 @@
         <v>129</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D97" s="1">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="E97" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="F97" s="2">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -3528,19 +3528,19 @@
         <v>9</v>
       </c>
       <c r="C98" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D98" s="1">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E98" s="1">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="F98" s="2">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="G98" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -3551,25 +3551,25 @@
         <v>131</v>
       </c>
       <c r="B99" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D99" s="1">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E99" s="1">
-        <v>46224</v>
+        <v>46229</v>
       </c>
       <c r="F99" s="2">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="G99" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -3577,25 +3577,25 @@
         <v>132</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C100" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="D100" s="1">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E100" s="1">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="F100" s="2">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="G100" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -3603,25 +3603,25 @@
         <v>133</v>
       </c>
       <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="1">
+        <v>46225</v>
+      </c>
+      <c r="E101" s="1">
+        <v>46230</v>
+      </c>
+      <c r="F101" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="G101" t="s">
         <v>22</v>
       </c>
-      <c r="C101" t="s">
-        <v>55</v>
-      </c>
-      <c r="D101" s="1">
-        <v>46223</v>
-      </c>
-      <c r="E101" s="1">
-        <v>46226</v>
-      </c>
-      <c r="F101" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="G101" t="s">
-        <v>11</v>
-      </c>
       <c r="H101" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -3629,25 +3629,25 @@
         <v>134</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D102" s="1">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="E102" s="1">
-        <v>46228</v>
+        <v>46252</v>
       </c>
       <c r="F102" s="2">
-        <v>4.9</v>
+        <v>27.2</v>
       </c>
       <c r="G102" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -3655,16 +3655,16 @@
         <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D103" s="1">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="E103" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="F103" s="2">
         <v>1.5</v>
@@ -3673,7 +3673,7 @@
         <v>11</v>
       </c>
       <c r="H103" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3681,10 +3681,10 @@
         <v>136</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D104" s="1">
         <v>46225</v>
@@ -3693,13 +3693,13 @@
         <v>46227</v>
       </c>
       <c r="F104" s="2">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="G104" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H104" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -3710,22 +3710,22 @@
         <v>9</v>
       </c>
       <c r="C105" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D105" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E105" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F105" s="2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G105" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H105" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -3733,25 +3733,25 @@
         <v>138</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D106" s="1">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E106" s="1">
-        <v>46229</v>
+        <v>46231</v>
       </c>
       <c r="F106" s="2">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
       </c>
       <c r="H106" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -3759,19 +3759,19 @@
         <v>139</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D107" s="1">
         <v>46226</v>
       </c>
       <c r="E107" s="1">
-        <v>46238</v>
+        <v>46231</v>
       </c>
       <c r="F107" s="2">
-        <v>12.2</v>
+        <v>4.7</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3785,25 +3785,25 @@
         <v>140</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D108" s="1">
         <v>46226</v>
       </c>
       <c r="E108" s="1">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="F108" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G108" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H108" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -3811,25 +3811,25 @@
         <v>141</v>
       </c>
       <c r="B109" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D109" s="1">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="E109" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="F109" s="2">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="G109" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H109" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -3840,22 +3840,22 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110" s="1">
+        <v>46230</v>
+      </c>
+      <c r="E110" s="1">
+        <v>46235</v>
+      </c>
+      <c r="F110" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="G110" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" t="s">
         <v>19</v>
-      </c>
-      <c r="D110" s="1">
-        <v>46227</v>
-      </c>
-      <c r="E110" s="1">
-        <v>46232</v>
-      </c>
-      <c r="F110" s="2">
-        <v>4.9</v>
-      </c>
-      <c r="G110" t="s">
-        <v>14</v>
-      </c>
-      <c r="H110" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3863,22 +3863,22 @@
         <v>143</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D111" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="E111" s="1">
-        <v>46229</v>
+        <v>46234</v>
       </c>
       <c r="F111" s="2">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="G111" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H111" t="s">
         <v>15</v>
@@ -3889,25 +3889,25 @@
         <v>144</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D112" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="E112" s="1">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="F112" s="2">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="G112" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H112" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -3915,19 +3915,19 @@
         <v>145</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C113" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D113" s="1">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="E113" s="1">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="F113" s="2">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -3944,19 +3944,19 @@
         <v>9</v>
       </c>
       <c r="C114" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D114" s="1">
         <v>46230</v>
       </c>
       <c r="E114" s="1">
-        <v>46235</v>
+        <v>46233</v>
       </c>
       <c r="F114" s="2">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="G114" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H114" t="s">
         <v>12</v>
@@ -3970,22 +3970,22 @@
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D115" s="1">
         <v>46230</v>
       </c>
       <c r="E115" s="1">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="F115" s="2">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="G115" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H115" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -3996,22 +3996,22 @@
         <v>9</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D116" s="1">
         <v>46230</v>
       </c>
       <c r="E116" s="1">
-        <v>46234</v>
+        <v>46236</v>
       </c>
       <c r="F116" s="2">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="G116" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -4022,22 +4022,22 @@
         <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D117" s="1">
         <v>46230</v>
       </c>
       <c r="E117" s="1">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="F117" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G117" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H117" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -4045,25 +4045,25 @@
         <v>150</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D118" s="1">
         <v>46230</v>
       </c>
       <c r="E118" s="1">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="F118" s="2">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="G118" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H118" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -4071,25 +4071,25 @@
         <v>151</v>
       </c>
       <c r="B119" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D119" s="1">
         <v>46230</v>
       </c>
       <c r="E119" s="1">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="F119" s="2">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="G119" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H119" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -4097,25 +4097,25 @@
         <v>152</v>
       </c>
       <c r="B120" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C120" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D120" s="1">
         <v>46230</v>
       </c>
       <c r="E120" s="1">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="F120" s="2">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="G120" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H120" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -4123,25 +4123,25 @@
         <v>153</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D121" s="1">
         <v>46230</v>
       </c>
       <c r="E121" s="1">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="F121" s="2">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="G121" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H121" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -4149,7 +4149,7 @@
         <v>154</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C122" t="s">
         <v>31</v>
@@ -4158,16 +4158,16 @@
         <v>46230</v>
       </c>
       <c r="E122" s="1">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="F122" s="2">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="G122" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H122" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -4175,25 +4175,25 @@
         <v>155</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C123" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D123" s="1">
         <v>46230</v>
       </c>
       <c r="E123" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="F123" s="2">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="G123" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H123" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -4201,25 +4201,25 @@
         <v>156</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D124" s="1">
         <v>46230</v>
       </c>
       <c r="E124" s="1">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="F124" s="2">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="G124" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H124" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -4227,25 +4227,25 @@
         <v>157</v>
       </c>
       <c r="B125" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C125" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D125" s="1">
         <v>46230</v>
       </c>
       <c r="E125" s="1">
-        <v>46238</v>
+        <v>46233</v>
       </c>
       <c r="F125" s="2">
-        <v>8.3</v>
+        <v>2.9</v>
       </c>
       <c r="G125" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H125" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -4253,22 +4253,22 @@
         <v>158</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D126" s="1">
         <v>46230</v>
       </c>
       <c r="E126" s="1">
-        <v>46241</v>
+        <v>46232</v>
       </c>
       <c r="F126" s="2">
-        <v>11.2</v>
+        <v>2.3</v>
       </c>
       <c r="G126" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H126" t="s">
         <v>12</v>
@@ -4279,22 +4279,22 @@
         <v>159</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D127" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E127" s="1">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="F127" s="2">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="G127" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H127" t="s">
         <v>12</v>
@@ -4305,22 +4305,22 @@
         <v>160</v>
       </c>
       <c r="B128" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C128" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D128" s="1">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E128" s="1">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F128" s="2">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G128" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H128" t="s">
         <v>12</v>
@@ -4331,25 +4331,25 @@
         <v>161</v>
       </c>
       <c r="B129" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D129" s="1">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="E129" s="1">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="F129" s="2">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="G129" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H129" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4357,25 +4357,25 @@
         <v>162</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D130" s="1">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="E130" s="1">
-        <v>46243</v>
+        <v>46235</v>
       </c>
       <c r="F130" s="2">
-        <v>12.3</v>
+        <v>3.2</v>
       </c>
       <c r="G130" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H130" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4383,25 +4383,25 @@
         <v>163</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D131" s="1">
         <v>46232</v>
       </c>
       <c r="E131" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="F131" s="2">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="G131" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H131" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -4409,25 +4409,25 @@
         <v>164</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C132" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D132" s="1">
         <v>46232</v>
       </c>
       <c r="E132" s="1">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="F132" s="2">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="G132" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H132" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -4438,22 +4438,22 @@
         <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D133" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E133" s="1">
-        <v>46237</v>
+        <v>46236</v>
       </c>
       <c r="F133" s="2">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
       </c>
       <c r="H133" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -4461,22 +4461,22 @@
         <v>166</v>
       </c>
       <c r="B134" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" t="s">
+        <v>10</v>
+      </c>
+      <c r="D134" s="1">
+        <v>46233</v>
+      </c>
+      <c r="E134" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F134" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="G134" t="s">
         <v>22</v>
-      </c>
-      <c r="C134" t="s">
-        <v>57</v>
-      </c>
-      <c r="D134" s="1">
-        <v>46232</v>
-      </c>
-      <c r="E134" s="1">
-        <v>46236</v>
-      </c>
-      <c r="F134" s="2">
-        <v>4.1</v>
-      </c>
-      <c r="G134" t="s">
-        <v>14</v>
       </c>
       <c r="H134" t="s">
         <v>15</v>
@@ -4487,25 +4487,25 @@
         <v>167</v>
       </c>
       <c r="B135" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D135" s="1">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="E135" s="1">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="F135" s="2">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="G135" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H135" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4516,7 +4516,7 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D136" s="1">
         <v>46233</v>
@@ -4528,10 +4528,10 @@
         <v>6</v>
       </c>
       <c r="G136" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H136" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4539,10 +4539,10 @@
         <v>169</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="D137" s="1">
         <v>46233</v>
@@ -4551,13 +4551,13 @@
         <v>46236</v>
       </c>
       <c r="F137" s="2">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G137" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H137" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -4565,25 +4565,25 @@
         <v>170</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C138" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D138" s="1">
         <v>46233</v>
       </c>
       <c r="E138" s="1">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F138" s="2">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="G138" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H138" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4591,25 +4591,25 @@
         <v>171</v>
       </c>
       <c r="B139" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C139" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D139" s="1">
         <v>46233</v>
       </c>
       <c r="E139" s="1">
-        <v>46236</v>
+        <v>46235</v>
       </c>
       <c r="F139" s="2">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G139" t="s">
         <v>11</v>
       </c>
       <c r="H139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -4617,25 +4617,25 @@
         <v>172</v>
       </c>
       <c r="B140" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D140" s="1">
         <v>46233</v>
       </c>
       <c r="E140" s="1">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="F140" s="2">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="G140" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H140" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4643,25 +4643,25 @@
         <v>173</v>
       </c>
       <c r="B141" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C141" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D141" s="1">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E141" s="1">
         <v>46237</v>
       </c>
       <c r="F141" s="2">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G141" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H141" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4669,25 +4669,25 @@
         <v>174</v>
       </c>
       <c r="B142" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C142" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="D142" s="1">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="E142" s="1">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="F142" s="2">
         <v>3.2</v>
       </c>
       <c r="G142" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H142" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4695,25 +4695,25 @@
         <v>175</v>
       </c>
       <c r="B143" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" t="s">
+        <v>78</v>
+      </c>
+      <c r="D143" s="1">
+        <v>46234</v>
+      </c>
+      <c r="E143" s="1">
+        <v>46235</v>
+      </c>
+      <c r="F143" s="2">
+        <v>1</v>
+      </c>
+      <c r="G143" t="s">
         <v>22</v>
       </c>
-      <c r="C143" t="s">
-        <v>23</v>
-      </c>
-      <c r="D143" s="1">
-        <v>46233</v>
-      </c>
-      <c r="E143" s="1">
-        <v>46236</v>
-      </c>
-      <c r="F143" s="2">
-        <v>2.9</v>
-      </c>
-      <c r="G143" t="s">
-        <v>11</v>
-      </c>
       <c r="H143" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4721,10 +4721,10 @@
         <v>176</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C144" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D144" s="1">
         <v>46234</v>
@@ -4736,10 +4736,10 @@
         <v>4.7</v>
       </c>
       <c r="G144" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H144" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
